--- a/docs/excel/04-bitacora-planilla.xlsx
+++ b/docs/excel/04-bitacora-planilla.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Bitácora (docs/99) y gestión de incidentes (docs/04, INC-2026-001..003); esta planilla y el registro de activos.</t>
+          <t>Bitácora (docs/99) y gestión de incidentes (docs/04, INC-2026-001..003); Excel de bitácora, registro de activos (A01-A22) y matriz RACI (16 procesos).</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Borradores. Commit 0ba84e1; planillas en el commit siguiente</t>
+          <t>Borradores. Commits 0ba84e1, b3ba156 y siguiente</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">

--- a/docs/excel/04-bitacora-planilla.xlsx
+++ b/docs/excel/04-bitacora-planilla.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Bitácora" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bitácora'!$A$1:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bitácora'!$A$1:$I$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -474,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1032,8 +1033,53 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Blue — Documentación</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>fmq203</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Excel 01 de controles MCU (47 controles + resumen) y documentos ISACA 01 política, 03 riesgos, 07 monitoreo, 09 accesos.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Borradores</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Mismo día. Brechas nuevas: Suricata sin ruleset público, sin retención 90 d, imágenes :latest, egress sin restringir, MFA del dashboard de Wazuh sin camino definido.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I12"/>
+  <autoFilter ref="A1:I13"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,N"</formula1>

--- a/docs/excel/04-bitacora-planilla.xlsx
+++ b/docs/excel/04-bitacora-planilla.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Bitácora" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bitácora'!$A$1:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bitácora'!$A$1:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1078,8 +1078,53 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Blue — Documentación</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>fmq203</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Kit de captura de evidencias (docs/evidencias/README.md); documentos 06 continuidad, 11 SoA (Anexo A completo, 93 controles), 12 notificación (ejercicio de escritorio INC-2026-004). Push al repo compartido.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>git push</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Borradores</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Mismo día. Evidencia no capturada (sin acceso de shell a docker-host desde la sesión). Sin respaldos de datos (RF-13). Plantilla SoA dice 79 controles; son 93.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I13"/>
+  <autoFilter ref="A1:I14"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"S,N"</formula1>

--- a/docs/excel/04-bitacora-planilla.xlsx
+++ b/docs/excel/04-bitacora-planilla.xlsx
@@ -20,7 +20,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1123,6 +1123,186 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Blue — Implementación/Prueba</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>fmq203</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Despliegue de CU-02 + Cowrie en el entorno de referencia; reglas OPNsense OPT2/OPT3</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>pct exec 108; nc -zv; ip neigh; OPNsense</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Éxito: agente ssh-client Active (ID 001), FIM/SCA/rootcheck</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Mismo día. CU-02 nunca había estado desplegado; reglas FW faltantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Blue — Implementación/Prueba</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Renzo Rampoldi</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Evidencia CU-01/02/03; CU-03 implementado (web-victim, FIM, regla 100200, isolate-webapp); TOTP Keycloak</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>nmap; fuerza bruta SSH; alta de .php en webroot</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>CU-01/02/03 detección+respuesta verificadas — 40364c8</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Carga diferida. Sin captura de mail; CU-02 con usuario inexistente</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Blue — Prueba/Documentación</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>fmq203</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Cierre de la notificación por mail de CU-02 y CU-03 de punta a punta</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>pct exec; compose --force-recreate; configure-manager.sh; postconf</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Éxito: CU-02 (MTTD~13s) y CU-03 (MTTD/MTTR~0s) con mail — e5f5541, 0925f6b, fcd653b</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Mismo día. Mail caído 14d (FW Gestión→DMZ 25 + postscreen/mynetworks); agente webapp reenrolado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Blue — Documentación</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>fmq203</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Diagramas Mermaid (00-arquitectura, infra/README) y revisión de documentación al estado real</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Docs alineadas — 29f89ae..a2f41a5</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Mismo día. Mermaid no admite puntos en etiquetas de flechas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I14"/>
   <dataValidations count="1">
